--- a/backend/templates/PurchaseOrder-JMC.xlsx
+++ b/backend/templates/PurchaseOrder-JMC.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\erp\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CA2C178-E3F8-4E09-9602-D03010467F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C86FB72-0B38-4780-ADB1-054CC109A885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2400" windowHeight="585" xr2:uid="{0B8F0BAC-6A3F-49EC-9CB4-F23E21491DF7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2400" windowHeight="585" xr2:uid="{FF536DEA-5666-4798-806D-C29EA0F03388}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$32</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1 (2)'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet1 (2)'!$1:$9</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" concurrentCalc="0"/>
   <extLst>
@@ -37,67 +37,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
-  <si>
-    <r>
-      <t xml:space="preserve">东莞市锦名诚电子有限公司
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">东莞市常平镇桥沥马屋村捷安科技园C栋202号
-TEL：0769-87187030   FAX：0769-87187029
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>采  购  单</t>
-    </r>
-  </si>
-  <si>
-    <t>采购单编号：PO-259203P</t>
-  </si>
-  <si>
-    <t>TO:彩智翔包装制品有限公司</t>
-  </si>
-  <si>
-    <t>FROM:东莞市锦名诚电子有限公司</t>
-  </si>
-  <si>
-    <t>ATTN:李小姐</t>
-  </si>
-  <si>
-    <t>下单日期：2026.01.15</t>
-  </si>
-  <si>
-    <t>TEL:13711951119</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+  <si>
+    <t>TO:盈黔橡胶</t>
+  </si>
+  <si>
+    <t>ATTN:王先生</t>
+  </si>
+  <si>
+    <t>TEL:13728253593</t>
   </si>
   <si>
     <t>TEL:0769-87187030</t>
   </si>
   <si>
-    <t>FAX:0769-82607832</t>
-  </si>
-  <si>
-    <t>适用机型：CSP_V3</t>
-  </si>
-  <si>
-    <t>FAX</t>
-  </si>
-  <si>
-    <t>E-mail:xinhua2009@vip.163.com</t>
-  </si>
-  <si>
-    <t>E-mail:</t>
+    <t>FAX:0769-87707179</t>
+  </si>
+  <si>
+    <t>E-mail:china094@126.com</t>
   </si>
   <si>
     <t>币别：人民币</t>
@@ -106,7 +63,7 @@
     <t>序号</t>
   </si>
   <si>
-    <t>产品  编号</t>
+    <t>产品编号</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -118,36 +75,24 @@
     <t>材质</t>
   </si>
   <si>
-    <t>表面   处理</t>
+    <t>表面处理</t>
   </si>
   <si>
     <t>单位</t>
   </si>
   <si>
+    <t>用量</t>
+  </si>
+  <si>
     <t>数量</t>
   </si>
   <si>
-    <t>产品单价</t>
-  </si>
-  <si>
-    <t>总价</t>
+    <t>产品  单价</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>F Logo</t>
-  </si>
-  <si>
-    <t>按最后样板</t>
-  </si>
-  <si>
-    <t>pcs</t>
-  </si>
-  <si>
-    <t>2026.03.15交货</t>
-  </si>
-  <si>
     <t>金额合计（小写）</t>
   </si>
   <si>
@@ -184,7 +129,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">                   1.2  </t>
+      <t xml:space="preserve">     2</t>
     </r>
     <r>
       <rPr>
@@ -192,12 +137,12 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>付款方式：月结30天；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">                   1.3  </t>
+      <t>、品质：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    2.1 </t>
     </r>
     <r>
       <rPr>
@@ -205,7 +150,20 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>以上报价为不含</t>
+      <t>产品生产按我司的工程图或合格样品及所规定之要求进行生产加工；</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    2.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>检验方法：我司分为全检和抽检两种方式，抽检按</t>
     </r>
     <r>
       <rPr>
@@ -213,7 +171,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>13%</t>
+      <t>MIL-STD-105E</t>
     </r>
     <r>
       <rPr>
@@ -221,12 +179,12 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>增值税；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">     2</t>
+      <t>二级正常单次抽样计划表进行检验；</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2.3 </t>
     </r>
     <r>
       <rPr>
@@ -234,33 +192,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>、品质：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">                    2.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>产品生产按我司的工程图或合格样品及所规定之要求进行生产加工；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">                    2.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>检验方法：我司分为全检和抽检两种方式，抽检按MIL-STD-105E二级正常单次抽样计划表进行检验；</t>
+      <t>所有材料必须符合环保要求</t>
     </r>
   </si>
   <si>
@@ -328,14 +260,24 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>交货时请在送货单上注明订单号码、产品编号、产品名称，在卸货时按我司仓管的要求对产品进行合理摆放。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">     供应商确认栏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         东莞市锦名诚电子有限公司</t>
+      <t>交货时请在送货单上注明订单号码、产品编号、产品名称，在卸货时按我司仓管的要求对产品进行合理摆放；</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                    3.3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请务必在承认交货时间前交货，若因延期交货导致我司交货延迟，后果由贵司承担；</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    供应商确认栏</t>
   </si>
   <si>
     <r>
@@ -372,7 +314,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">    袁小琼    </t>
+      <t xml:space="preserve">   袁小琼    </t>
     </r>
     <r>
       <rPr>
@@ -420,7 +362,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">              </t>
+      <t xml:space="preserve">             </t>
     </r>
     <r>
       <rPr>
@@ -432,29 +374,151 @@
       </rPr>
       <t>1</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">东莞市锦名诚电子有限公司
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">东莞市常平镇桥沥马屋村捷安科技园C栋202号
+TEL：0769-87187030  FAX：0769-87187029
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>采   购   单</t>
+    </r>
+  </si>
+  <si>
+    <t>采购单编号：JMC20210966H</t>
+  </si>
+  <si>
+    <t>下单日期：2024.01.03</t>
+  </si>
+  <si>
+    <r>
+      <t>FROM:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东莞市锦名诚电子有限公司</t>
+    </r>
+  </si>
+  <si>
+    <t>适用机型：CSS SQ</t>
+  </si>
+  <si>
+    <t>E-mail:business@jmc-metal.com</t>
+  </si>
+  <si>
+    <t>金额</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                   1.2  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>付款方式：月结</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0天；</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                   1.3  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以上报价为不含</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>13%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增值税；</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">      东莞市锦名诚电子有限公司</t>
+  </si>
+  <si>
+    <t>3.4 交货时间：</t>
+    <phoneticPr fontId="23" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
-    <numFmt numFmtId="7" formatCode="&quot;¥&quot;#,##0.00;&quot;¥&quot;\-#,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="6">
     <numFmt numFmtId="177" formatCode="0.000_ "/>
     <numFmt numFmtId="178" formatCode="0.0000_ "/>
     <numFmt numFmtId="179" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="180" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="&quot;¥&quot;#,##0.00_);\(&quot;¥&quot;#,##0.00\)"/>
     <numFmt numFmtId="181" formatCode="[DBNum2][$RMB]General;[Red][DBNum2][$RMB]General"/>
     <numFmt numFmtId="182" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -480,9 +544,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color indexed="12"/>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -497,6 +559,37 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -505,6 +598,18 @@
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -532,15 +637,21 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -618,6 +729,30 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -641,187 +776,278 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -902,6 +1128,307 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>390525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76856" name="Picture 26" descr="CSS-064_dust cover_002">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2794D1DD-C062-3671-7A11-2CEE4D4BEAA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1323975" y="3114675"/>
+          <a:ext cx="542925" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>695325</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>428625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76857" name="Picture 1115">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7AF3C80-12BD-4DA7-AA0D-5187B8DDF547}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1285875" y="4038600"/>
+          <a:ext cx="638175" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>409575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76858" name="Picture 18905">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB19438C-B7BC-7B47-567D-1D4CBD82C66F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1314450" y="3571875"/>
+          <a:ext cx="571500" cy="361950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>361950</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76859" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFAFF647-60BB-E1D9-02C0-DEE84CA3FFC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7200900" y="1609725"/>
+          <a:ext cx="5572125" cy="2743200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1155,577 +1682,616 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr>
+        <a:gradFill rotWithShape="0">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="BBD5F0"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="9CBEE0"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000"/>
+          <a:tileRect/>
+        </a:gradFill>
+        <a:ln w="15875" cap="flat" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="739CC3"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </a:spPr>
+      <a:bodyPr/>
+      <a:lstStyle/>
+    </a:spDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C910098C-00A8-49EB-8AEF-032977CD9034}">
-  <dimension ref="A1:S31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FCC3733-298A-407F-A42B-61481981F733}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="8" style="4" customWidth="1"/>
-    <col min="9" max="9" width="9" style="4" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="5.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="4.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="8" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="101.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:16" ht="98.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+    </row>
+    <row r="2" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="11"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+    </row>
+    <row r="3" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-    </row>
-    <row r="2" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="43" t="s">
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+    </row>
+    <row r="4" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-    </row>
-    <row r="3" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44" t="s">
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+    </row>
+    <row r="5" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="43" t="s">
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-    </row>
-    <row r="4" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="44" t="s">
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+    </row>
+    <row r="6" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="45" t="s">
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="88" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+    </row>
+    <row r="7" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-    </row>
-    <row r="5" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="46" t="s">
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="88"/>
+      <c r="L7" s="88"/>
+    </row>
+    <row r="8" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="45" t="s">
+      <c r="K8" s="71"/>
+      <c r="L8" s="72"/>
+      <c r="N8" s="17"/>
+    </row>
+    <row r="9" spans="1:16" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
+      <c r="B9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="45" t="s">
+      <c r="C9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="45" t="s">
+      <c r="D9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="45"/>
-    </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="44" t="s">
+      <c r="E9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="45" t="s">
+      <c r="F9" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-    </row>
-    <row r="8" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="47" t="s">
+      <c r="G9" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="48"/>
-      <c r="K8" s="49"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-    </row>
-    <row r="9" spans="1:19" s="1" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="H9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="I9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="J9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="K9" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="12" t="s">
+    </row>
+    <row r="10" spans="1:16" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="22"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="31"/>
+    </row>
+    <row r="11" spans="1:16" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="22"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="85"/>
+    </row>
+    <row r="12" spans="1:16" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="22"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="85"/>
+    </row>
+    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="74">
+        <f>SUM(K10:K12)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="75"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="40"/>
+    </row>
+    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="I14" s="76"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="77">
+        <f>K13</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="78"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="40"/>
+    </row>
+    <row r="15" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+    </row>
+    <row r="19" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+    </row>
+    <row r="20" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+    </row>
+    <row r="21" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="52" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" s="39" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12">
-        <v>1</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16" t="s">
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+    </row>
+    <row r="22" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+    </row>
+    <row r="23" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="52"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18" t="s">
+      <c r="D23" s="53"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+    </row>
+    <row r="24" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="19">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="20">
-        <v>0.7</v>
-      </c>
-      <c r="J10" s="20">
-        <f>H10*I10</f>
-        <v>7000</v>
-      </c>
-      <c r="K10" s="21" t="s">
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+    </row>
+    <row r="25" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="47" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" s="40" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="27"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="28"/>
-    </row>
-    <row r="12" spans="1:19" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="50" t="s">
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+    </row>
+    <row r="26" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="51">
-        <f>J10</f>
-        <v>7000</v>
-      </c>
-      <c r="K12" s="52"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="28"/>
-    </row>
-    <row r="13" spans="1:19" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="50" t="s">
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+    </row>
+    <row r="27" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="53">
-        <f>J12</f>
-        <v>7000</v>
-      </c>
-      <c r="K13" s="54"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="28"/>
-    </row>
-    <row r="14" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="30" t="s">
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+    </row>
+    <row r="28" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-    </row>
-    <row r="15" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="55"/>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:12" s="4" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+    </row>
+    <row r="30" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="52"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="53"/>
+    </row>
+    <row r="31" spans="1:12" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-    </row>
-    <row r="16" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="32" t="s">
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="62"/>
+      <c r="J31" s="62" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="63"/>
+      <c r="B32" s="63"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="64"/>
+      <c r="I32" s="62"/>
+    </row>
+    <row r="33" spans="1:10" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-    </row>
-    <row r="17" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="33" t="s">
+      <c r="C33" s="62"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="63"/>
+      <c r="J33" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-    </row>
-    <row r="18" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="32" t="s">
+    </row>
+    <row r="34" spans="1:10" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-    </row>
-    <row r="19" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="34" t="s">
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="63"/>
+      <c r="J34" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-    </row>
-    <row r="20" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-    </row>
-    <row r="21" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-    </row>
-    <row r="22" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-    </row>
-    <row r="23" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-    </row>
-    <row r="24" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-    </row>
-    <row r="25" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-    </row>
-    <row r="26" spans="1:11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="32"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-    </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="36"/>
-      <c r="H27" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" s="35"/>
-    </row>
-    <row r="28" spans="1:11" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="37"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="37"/>
-    </row>
-    <row r="29" spans="1:11" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="I29" s="38" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="I30" s="38" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="55"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="56"/>
-      <c r="K31" s="56"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A31:K31"/>
+  <mergeCells count="21">
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="J6:L6"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="J2:L2"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="J3:L3"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" xr:uid="{D0E0FA5C-714B-4F34-A334-F09403394E94}"/>
-  </hyperlinks>
+  <phoneticPr fontId="23" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.20069444444444445" right="0.20069444444444445" top="0.59027777777777779" bottom="0.59444444444444444" header="0.51180555555555551" footer="0.31458333333333333"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageMargins left="0.2" right="0.2" top="0.39" bottom="0.2" header="0.51" footer="0.31"/>
+  <pageSetup paperSize="9" scale="56" orientation="landscape" r:id="rId1"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddFooter>&amp;C第 &amp;P 页，共 &amp;N 页</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/backend/templates/PurchaseOrder-JMC.xlsx
+++ b/backend/templates/PurchaseOrder-JMC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\erp\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C86FB72-0B38-4780-ADB1-054CC109A885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35236781-37F5-441A-B577-8239BC36A130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="2400" windowHeight="585" xr2:uid="{FF536DEA-5666-4798-806D-C29EA0F03388}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1 (2)'!$A$1:$L$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet1 (2)'!$1:$9</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -404,22 +404,6 @@
     <t>采购单编号：JMC20210966H</t>
   </si>
   <si>
-    <t>下单日期：2024.01.03</t>
-  </si>
-  <si>
-    <r>
-      <t>FROM:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东莞市锦名诚电子有限公司</t>
-    </r>
-  </si>
-  <si>
     <t>适用机型：CSS SQ</t>
   </si>
   <si>
@@ -490,7 +474,13 @@
     <t xml:space="preserve">      东莞市锦名诚电子有限公司</t>
   </si>
   <si>
-    <t>3.4 交货时间：</t>
+    <t>FROM:东莞市锦名诚电子有限公司</t>
+  </si>
+  <si>
+    <t>下单日期：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                   3.4 交货时间：</t>
     <phoneticPr fontId="23" type="noConversion"/>
   </si>
 </sst>
@@ -499,12 +489,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="0.0000_ "/>
-    <numFmt numFmtId="179" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="180" formatCode="&quot;¥&quot;#,##0.00_);\(&quot;¥&quot;#,##0.00\)"/>
-    <numFmt numFmtId="181" formatCode="[DBNum2][$RMB]General;[Red][DBNum2][$RMB]General"/>
-    <numFmt numFmtId="182" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
+    <numFmt numFmtId="178" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="179" formatCode="&quot;¥&quot;#,##0.00_);\(&quot;¥&quot;#,##0.00\)"/>
+    <numFmt numFmtId="180" formatCode="[DBNum2][$RMB]General;[Red][DBNum2][$RMB]General"/>
+    <numFmt numFmtId="181" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -779,271 +769,223 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1719,555 +1661,562 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="4.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="5" customWidth="1"/>
     <col min="7" max="7" width="4.5703125" style="2" customWidth="1"/>
     <col min="8" max="8" width="5.140625" style="2" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" customWidth="1"/>
     <col min="10" max="10" width="6.85546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="11.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="6" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="98.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:15" ht="98.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-    </row>
-    <row r="2" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="86" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+    </row>
+    <row r="2" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-    </row>
-    <row r="3" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+    </row>
+    <row r="3" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="69" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+    </row>
+    <row r="4" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+    </row>
+    <row r="5" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+    </row>
+    <row r="6" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-    </row>
-    <row r="4" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="69" t="s">
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+    </row>
+    <row r="7" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-    </row>
-    <row r="5" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="88" t="s">
-        <v>3</v>
-      </c>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-    </row>
-    <row r="6" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="88" t="s">
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+    </row>
+    <row r="8" spans="1:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="54"/>
+      <c r="L8" s="55"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:15" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-    </row>
-    <row r="7" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="69" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-    </row>
-    <row r="8" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="70" t="s">
-        <v>6</v>
-      </c>
-      <c r="K8" s="71"/>
-      <c r="L8" s="72"/>
-      <c r="N8" s="17"/>
-    </row>
-    <row r="9" spans="1:16" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="21" t="s">
+      <c r="L9" s="19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="31"/>
-    </row>
-    <row r="11" spans="1:16" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="84"/>
-      <c r="L11" s="85"/>
-    </row>
-    <row r="12" spans="1:16" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="85"/>
-    </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="73" t="s">
+    <row r="10" spans="1:15" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="27"/>
+    </row>
+    <row r="11" spans="1:15" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="65"/>
+    </row>
+    <row r="12" spans="1:15" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="65"/>
+    </row>
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
-      <c r="K13" s="74">
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="57">
         <f>SUM(K10:K12)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="75"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="40"/>
-    </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="76" t="s">
+      <c r="L13" s="58"/>
+      <c r="O13" s="34"/>
+    </row>
+    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="77">
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="59">
         <f>K13</f>
         <v>0</v>
       </c>
-      <c r="L14" s="78"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="40"/>
-    </row>
-    <row r="15" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="41" t="s">
+      <c r="L14" s="60"/>
+      <c r="O14" s="34"/>
+    </row>
+    <row r="15" spans="1:15" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="42" t="s">
+    <row r="16" spans="1:15" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="45"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="39"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+    </row>
+    <row r="19" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+    </row>
+    <row r="20" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="35"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41"/>
+    </row>
+    <row r="25" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+    </row>
+    <row r="26" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="44"/>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="46"/>
+    </row>
+    <row r="30" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="36"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="35"/>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="1:12" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="50"/>
+      <c r="J31" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="47"/>
-    </row>
-    <row r="19" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
-    </row>
-    <row r="20" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-    </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-    </row>
-    <row r="22" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-    </row>
-    <row r="23" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="52"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="53"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-    </row>
-    <row r="24" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-    </row>
-    <row r="25" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-    </row>
-    <row r="26" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-    </row>
-    <row r="27" spans="1:12" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-    </row>
-    <row r="28" spans="1:12" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="55"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" s="4" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="57"/>
-    </row>
-    <row r="30" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="52"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="53"/>
-    </row>
-    <row r="31" spans="1:12" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="62"/>
-      <c r="J31" s="62" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="63"/>
-      <c r="B32" s="63"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="64"/>
-      <c r="I32" s="62"/>
-    </row>
-    <row r="33" spans="1:10" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="65" t="s">
+    </row>
+    <row r="32" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="51"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="52"/>
+      <c r="I32" s="50"/>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="1:10" s="2" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="62"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="63"/>
-      <c r="J33" s="65" t="s">
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="51"/>
+      <c r="J33" s="49" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="65" t="s">
+    <row r="34" spans="1:10" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="63"/>
-      <c r="J34" s="65" t="s">
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="51"/>
+      <c r="J34" s="49" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="J4:L4"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
@@ -2278,12 +2227,11 @@
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="J7:L7"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:L14"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/backend/templates/PurchaseOrder-JMC.xlsx
+++ b/backend/templates/PurchaseOrder-JMC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\erp\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35236781-37F5-441A-B577-8239BC36A130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF65FA6E-872B-4E2B-BFD9-E2497A67D8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="2400" windowHeight="585" xr2:uid="{FF536DEA-5666-4798-806D-C29EA0F03388}"/>
   </bookViews>
@@ -927,6 +927,42 @@
     <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -950,42 +986,6 @@
     </xf>
     <xf numFmtId="180" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1070,307 +1070,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76856" name="Picture 26" descr="CSS-064_dust cover_002">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2794D1DD-C062-3671-7A11-2CEE4D4BEAA4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1323975" y="3114675"/>
-          <a:ext cx="542925" cy="333375"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>695325</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>428625</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76857" name="Picture 1115">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7AF3C80-12BD-4DA7-AA0D-5187B8DDF547}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1285875" y="4038600"/>
-          <a:ext cx="638175" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>409575</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76858" name="Picture 18905">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB19438C-B7BC-7B47-567D-1D4CBD82C66F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1314450" y="3571875"/>
-          <a:ext cx="571500" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>361950</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76859" name="图片 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFAFF647-60BB-E1D9-02C0-DEE84CA3FFC6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="7200900" y="1609725"/>
-          <a:ext cx="5572125" cy="2743200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1680,20 +1379,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="98.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
     </row>
     <row r="2" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
@@ -1705,101 +1404,101 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
-      <c r="J2" s="71" t="s">
+      <c r="J2" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
     </row>
     <row r="3" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
       <c r="E3" s="10"/>
       <c r="F3" s="8"/>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
-      <c r="J3" s="66" t="s">
+      <c r="J3" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
     </row>
     <row r="4" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
       <c r="E4" s="10"/>
       <c r="F4" s="8"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="66" t="s">
+      <c r="J4" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
     </row>
     <row r="5" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="10"/>
       <c r="F5" s="8"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
-      <c r="J5" s="67" t="s">
+      <c r="J5" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
     </row>
     <row r="6" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="10"/>
       <c r="F6" s="8"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="67" t="s">
+      <c r="J6" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
     </row>
     <row r="7" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
       <c r="E7" s="10"/>
       <c r="F7" s="8"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
-      <c r="J7" s="67" t="s">
+      <c r="J7" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
     </row>
     <row r="8" spans="1:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11"/>
@@ -1811,11 +1510,11 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="53" t="s">
+      <c r="J8" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="54"/>
-      <c r="L8" s="55"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="67"/>
       <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1877,12 +1576,12 @@
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
       <c r="F11" s="23"/>
-      <c r="G11" s="61"/>
+      <c r="G11" s="59"/>
       <c r="H11" s="17"/>
       <c r="I11" s="25"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="65"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="63"/>
     </row>
     <row r="12" spans="1:15" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="20"/>
@@ -1891,12 +1590,12 @@
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
-      <c r="G12" s="62"/>
+      <c r="G12" s="60"/>
       <c r="H12" s="17"/>
       <c r="I12" s="25"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="65"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28"/>
@@ -1906,16 +1605,16 @@
       <c r="E13" s="20"/>
       <c r="F13" s="32"/>
       <c r="G13" s="33"/>
-      <c r="H13" s="56" t="s">
+      <c r="H13" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="57">
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="69">
         <f>SUM(K10:K12)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="58"/>
+      <c r="L13" s="70"/>
       <c r="O13" s="34"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1926,16 +1625,16 @@
       <c r="E14" s="20"/>
       <c r="F14" s="32"/>
       <c r="G14" s="33"/>
-      <c r="H14" s="56" t="s">
+      <c r="H14" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="59">
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="71">
         <f>K13</f>
         <v>0</v>
       </c>
-      <c r="L14" s="60"/>
+      <c r="L14" s="72"/>
       <c r="O14" s="34"/>
     </row>
     <row r="15" spans="1:15" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2211,12 +1910,10 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:L14"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
@@ -2228,10 +1925,12 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -2240,6 +1939,5 @@
   <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddFooter>&amp;C第 &amp;P 页，共 &amp;N 页</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>